--- a/employee.xlsx
+++ b/employee.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8BC042E-391C-48A1-BE1F-3AED0B759AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5590230-16B9-4FB0-8DCD-0440B6BCB364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
   <si>
     <t>Empid</t>
   </si>
@@ -117,13 +118,31 @@
   </si>
   <si>
     <t>total salary</t>
+  </si>
+  <si>
+    <t>number of emp</t>
+  </si>
+  <si>
+    <t>avg of the emp</t>
+  </si>
+  <si>
+    <t>find the sum of salary of the employess whos city= mumbai</t>
+  </si>
+  <si>
+    <t>find the sum of salary of those employe whoes age &lt; 25 and city mumbai</t>
+  </si>
+  <si>
+    <t>the employe age greater then 25 sumif</t>
+  </si>
+  <si>
+    <t>sumifs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +159,14 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -198,6 +225,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -711,8 +739,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D12">
@@ -720,7 +748,287 @@
         <v>5725099.9000000004</v>
       </c>
     </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <f>COUNT(D2:D10)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <f>AVERAGE(D2:D10)</f>
+        <v>636122.2111111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899B7C6D-EFDE-4904-8BBA-72295E9C63D5}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45000.9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2">
+        <v>23000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
+        <v>510000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
+        <v>51000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>108</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>109</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4900099</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <f>SUMIF(F2:F10,"mumbai",D2:D10)</f>
+        <v>155000</v>
+      </c>
+      <c r="D13">
+        <f>D3+D5+D9</f>
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <f>SUMIF(C2:C10,"&gt;25",D2:D10)</f>
+        <v>5626099.9000000004</v>
+      </c>
+      <c r="D14">
+        <f>D10+D8+D7+D6+D4+D3+D2</f>
+        <v>5626099.9000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <f>SUMIFS(D2:D10,C2:C10,"&lt;25",F2:F10,"mumbai")</f>
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <f>AVERAGEIF(F2:F10,"mumbai",D2:D10)</f>
+        <v>51666.666666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/employee.xlsx
+++ b/employee.xlsx
@@ -8,13 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5590230-16B9-4FB0-8DCD-0440B6BCB364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637640E1-4261-4A9C-8CC0-893826DEE91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet7" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet8" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="85">
   <si>
     <t>Empid</t>
   </si>
@@ -136,13 +143,169 @@
   </si>
   <si>
     <t>sumifs</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">question </t>
+  </si>
+  <si>
+    <t>marks&gt;=75, grade A</t>
+  </si>
+  <si>
+    <t>otherwise fail</t>
+  </si>
+  <si>
+    <t>use multiple if else</t>
+  </si>
+  <si>
+    <t>marks&gt;=50, grade c</t>
+  </si>
+  <si>
+    <t>marks&gt;=60, grade b</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question : Checks Weather a student has passed all subject </t>
+  </si>
+  <si>
+    <t>Passing marks &gt;= 40 in all subject</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Question of OR function: Check weather a student have pass atleast in one subject</t>
+  </si>
+  <si>
+    <t>Passing marks &gt;=40</t>
+  </si>
+  <si>
+    <t>OR Function</t>
+  </si>
+  <si>
+    <t>Que: salary &gt;=50000 and city = mumbai then eligble for bonus otherwise not eligible</t>
+  </si>
+  <si>
+    <t>Que: salary &gt;=50000 or city = mumbai then eligble for bonus otherwise not eligible</t>
+  </si>
+  <si>
+    <t>Eligible For Bonus (AND)</t>
+  </si>
+  <si>
+    <t>Eligible For Bonus (OR)</t>
+  </si>
+  <si>
+    <t>meena pandey</t>
+  </si>
+  <si>
+    <t>ramesh sharma</t>
+  </si>
+  <si>
+    <t>renu agrawal</t>
+  </si>
+  <si>
+    <t>suresh pathak</t>
+  </si>
+  <si>
+    <t>ctrl + E - short cut key for flash fill</t>
+  </si>
+  <si>
+    <t>Meena</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>Renu</t>
+  </si>
+  <si>
+    <t>Pandey</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Agrawal</t>
+  </si>
+  <si>
+    <t>Pathak</t>
+  </si>
+  <si>
+    <t>Emp_id</t>
+  </si>
+  <si>
+    <t>MUMBAI</t>
+  </si>
+  <si>
+    <t>hyderabad</t>
+  </si>
+  <si>
+    <t>Channai</t>
+  </si>
+  <si>
+    <t>PUNE</t>
+  </si>
+  <si>
+    <t>HYderabad</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>mumbai</t>
+  </si>
+  <si>
+    <t>Update_city</t>
+  </si>
+  <si>
+    <t>BANGALORE</t>
+  </si>
+  <si>
+    <t>HYDERABAD</t>
+  </si>
+  <si>
+    <t>CHANNAI</t>
+  </si>
+  <si>
+    <t>daksh@gmail.com</t>
+  </si>
+  <si>
+    <t>gmail.com</t>
+  </si>
+  <si>
+    <t>ram112@tcs.com</t>
+  </si>
+  <si>
+    <t>ranu32@itvadent.com</t>
+  </si>
+  <si>
+    <t>Daksh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +331,63 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -187,7 +407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -210,11 +430,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -226,11 +458,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -241,6 +509,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C488D2FF-8C29-4D0B-873C-C3FE75F8F5B0}" name="Table1" displayName="Table1" ref="A1:C9" totalsRowShown="0">
+  <autoFilter ref="A1:C9" xr:uid="{C488D2FF-8C29-4D0B-873C-C3FE75F8F5B0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{978B9E58-9A06-45C0-A2AF-4328ABECE471}" name="Emp_id"/>
+    <tableColumn id="2" xr3:uid="{4D112869-DAA1-433C-BDC3-CC197ABF9A1D}" name="City"/>
+    <tableColumn id="3" xr3:uid="{CBA14845-D35D-4DE0-AD69-ADC159662A50}" name="Update_city" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,8 +1053,599 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A8A268-94D2-4ECC-BF4F-D2BA65E083C3}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45000.9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <f>IF(AND(D2&gt;=50000,F2="mumbai"),"eligible","not eligible")</f>
+        <v>not eligible</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <f>IF(OR(D2&gt;=50000,F2="mumbai"),"eligible","not eligible")</f>
+        <v>not eligible</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f t="shared" ref="G3:G10" si="0">IF(AND(D3&gt;=50000,F3="mumbai"),"eligible","not eligible")</f>
+        <v>eligible</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H10" si="1">IF(OR(D3&gt;=50000,F3="mumbai"),"eligible","not eligible")</f>
+        <v>eligible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2">
+        <v>23000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>not eligible</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>eligible</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
+        <v>510000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>eligible</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>not eligible</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
+        <v>51000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>eligible</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>108</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>eligible</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>eligible</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>109</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2">
+        <v>49000</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>not eligible</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>not eligible</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDD7475-B6BB-4F56-B768-897728F2955A}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+      <c r="B7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E77BFD4A-6D5D-4CD2-9F54-CAFC2E52AEB6}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFCC19D-9BA1-4D76-990B-003FF3A9969E}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="16">
+        <v>38525</v>
+      </c>
+      <c r="B1">
+        <v>2005</v>
+      </c>
+      <c r="C1">
+        <v>6</v>
+      </c>
+      <c r="D1" s="15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
+        <v>24672</v>
+      </c>
+      <c r="B2">
+        <v>1967</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>42909</v>
+      </c>
+      <c r="B3">
+        <v>2017</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="15">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E1ADA6-8A0E-4323-A8C2-B73DD299E8B6}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{7991A5AC-7138-47C4-AF51-778CF4DB7DB0}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{14EDAE5D-3128-4794-A0AE-F814971CDA94}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{5FB96FAD-3F1C-4696-A319-E8A069CCAABB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899B7C6D-EFDE-4904-8BBA-72295E9C63D5}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.5703125" customWidth="1"/>
@@ -784,7 +1655,7 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,8 +1674,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -824,7 +1698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>102</v>
       </c>
@@ -844,7 +1718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -864,7 +1738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>104</v>
       </c>
@@ -884,7 +1758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -904,7 +1778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>106</v>
       </c>
@@ -924,7 +1798,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>107</v>
       </c>
@@ -944,7 +1818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>108</v>
       </c>
@@ -964,7 +1838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>109</v>
       </c>
@@ -984,7 +1858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -997,7 +1871,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1010,7 +1884,7 @@
         <v>5626099.9000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1031,4 +1905,335 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{103216E0-8D69-4951-B44D-E6BD2BB2D2FE}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2">
+        <v>78</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>IF(B2&gt;=75,"A",IF(B2&gt;=60,"B",IF(B2&gt;=50,"C","fail")))</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3">
+        <v>90</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <f t="shared" ref="C3:C8" si="0">IF(B3&gt;=75,"A",IF(B3&gt;=60,"B",IF(B3&gt;=50,"C","fail")))</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>fail</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3">
+        <v>68</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="5:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA192E28-6D50-4460-9201-1A2BB326FDC7}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2">
+        <v>67</v>
+      </c>
+      <c r="D2" s="2">
+        <v>89</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <f>AND(B2&gt;=40,C2&gt;=40,D2&gt;=40)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <f>IF(AND(B2&gt;=40,C2&gt;=40,D2&gt;=40),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="G2" t="b">
+        <f>OR(B2&gt;=40,C2&gt;=40,D2&gt;=40)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3">
+        <v>67</v>
+      </c>
+      <c r="C3" s="3">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="b">
+        <f t="shared" ref="E3:E5" si="0">AND(B3&gt;=40,C3&gt;=40,D3&gt;=40)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f t="shared" ref="F3:F5" si="1">IF(AND(B3&gt;=40,C3&gt;=40,D3&gt;=40),"Pass","Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="G3" t="b">
+        <f t="shared" ref="G3:G5" si="2">OR(B3&gt;=40,C3&gt;=40,D3&gt;=40)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2">
+        <v>34</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+      <c r="G4" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3">
+        <v>67</v>
+      </c>
+      <c r="C5" s="3">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3">
+        <v>89</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+      <c r="G5" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="14" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B14:F14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>